--- a/Documentação/Product BackLog FilhosDoOlimpo.xlsx
+++ b/Documentação/Product BackLog FilhosDoOlimpo.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gusta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E979D4C-5EB2-4BF0-B63B-D81E5D5E7640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E924252-4D10-423C-A0ED-1C233DBEC5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11385" xr2:uid="{731633DF-1D25-49D1-98D9-40A0E5BC9201}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,20 +27,24 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="47">
   <si>
     <t>Requisito</t>
   </si>
   <si>
+    <t>Descrição</t>
+  </si>
+  <si>
     <t>Classificação</t>
   </si>
   <si>
@@ -50,62 +54,137 @@
     <t>Prioridade</t>
   </si>
   <si>
-    <t>Tela de Login e Cadastro</t>
-  </si>
-  <si>
     <t>ESSENCIAL</t>
   </si>
   <si>
+    <t>IMPORTANTE</t>
+  </si>
+  <si>
     <t>Alta</t>
   </si>
   <si>
-    <t>Página Home</t>
-  </si>
-  <si>
-    <t>Seção de Personagens</t>
-  </si>
-  <si>
-    <t>Seção de Deuses</t>
-  </si>
-  <si>
-    <t>Página para informações de personagens</t>
-  </si>
-  <si>
-    <t>Página para informações de deuses</t>
-  </si>
-  <si>
-    <t>Estilização de Login e Cadastro</t>
-  </si>
-  <si>
     <t>Média</t>
   </si>
   <si>
-    <t>Estilização da Página Home</t>
-  </si>
-  <si>
-    <t>Estilização da seção de personagens</t>
-  </si>
-  <si>
-    <t>Estilização da seção de deuses</t>
-  </si>
-  <si>
-    <t>Criação de temas individuais para cada deus</t>
-  </si>
-  <si>
-    <t>Criação da dashboard de cada deus</t>
-  </si>
-  <si>
-    <t>Validação de cadastro</t>
-  </si>
-  <si>
-    <t>Baixa</t>
+    <t>RF1 - Página Home</t>
+  </si>
+  <si>
+    <t>RF2 - Tela de Login e Cadastro</t>
+  </si>
+  <si>
+    <t>RNF2 - Estilização de Login e Cadastro</t>
+  </si>
+  <si>
+    <t>RNF1 - Estilização da Página Home</t>
+  </si>
+  <si>
+    <t>RNF3 - Criação de temas individuais para cada deus</t>
+  </si>
+  <si>
+    <t>RF3 - Validação de cadastro</t>
+  </si>
+  <si>
+    <t>RNF4 - Estilização da seção de personagens</t>
+  </si>
+  <si>
+    <t>RNF5 - Estilização da seção de deuses</t>
+  </si>
+  <si>
+    <t>RNF6 - Estilização das páginas de deuses</t>
+  </si>
+  <si>
+    <t>RNF7 - Estilização das páginas de personagens</t>
+  </si>
+  <si>
+    <t>RF4 - Validação de login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamanho </t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>RF5 - Criação da dashboard de cada deus</t>
+  </si>
+  <si>
+    <t>RF6 - Seção de Personagens</t>
+  </si>
+  <si>
+    <t>RF7 - Página para informações de personagens</t>
+  </si>
+  <si>
+    <t>RF8 - Seção de Deuses</t>
+  </si>
+  <si>
+    <t>RF9 - Página para informações de deuses</t>
+  </si>
+  <si>
+    <t>RF10 - Cálculo Matemático</t>
+  </si>
+  <si>
+    <t>Página que exibe informações de cada deus disponível</t>
+  </si>
+  <si>
+    <t>Página que exibe informações de cada personagem disponível</t>
+  </si>
+  <si>
+    <t>Criação da página de boas-vindas ao usuário</t>
+  </si>
+  <si>
+    <t>Criação da seção de personagens disponíveis no sistema</t>
+  </si>
+  <si>
+    <t>Criação da seção que contêm os deuses disponíveis no sistema</t>
+  </si>
+  <si>
+    <t>Criação do design da página de login e cadastro do usuário</t>
+  </si>
+  <si>
+    <t>Criação do design da página inicial</t>
+  </si>
+  <si>
+    <t>Criação da página de criação de usuário e login</t>
+  </si>
+  <si>
+    <t>Validação se a conta informada se encontra no banco de dados</t>
+  </si>
+  <si>
+    <t>Implementação de um cálculo matemático na Dashboard para soma de estatísticas de cada deus</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de uma dashboard que mostre as estatísticas individuais de cada deus disponível</t>
+  </si>
+  <si>
+    <t>Criação e desenvolvimento de um tema exclusivo para filhos de determinado deus</t>
+  </si>
+  <si>
+    <t>Desenvolvimento da identidade visual da seção de personagens</t>
+  </si>
+  <si>
+    <t>Desenvolvimento da identidade visual da seção de deuses</t>
+  </si>
+  <si>
+    <t>Desenvolvimento da interface visual das páginas de informações dos deuses</t>
+  </si>
+  <si>
+    <t>Desenvolvimento da interface visual das páginas de informações dos personagens</t>
+  </si>
+  <si>
+    <t>Verificação dos dados obrigatórios para criação de conta, como email válido e senha compatível</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,10 +193,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -129,14 +224,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FFBDD7EE"/>
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,12 +275,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -206,7 +305,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -502,212 +601,382 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4029971-58A3-46AA-938F-C2141AA06F0B}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" customWidth="1"/>
-    <col min="3" max="3" width="30.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+    <col min="1" max="1" width="48.5703125" customWidth="1"/>
+    <col min="2" max="2" width="94.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>8</v>
+        <v>32</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2" t="s">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="2">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="2">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>13</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>13</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
+      <c r="F18" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F18">
+    <sortCondition ref="E2:E18"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>